--- a/Checklist - Artefato 3.xlsx
+++ b/Checklist - Artefato 3.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rafael Fernandes\Downloads\ChecklistQualidade\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\A538841\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31059D23-A460-4F70-A289-8F58648E6605}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{74C7F7E2-BDC6-483A-9C0D-778CA7AAFA45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{AD0D3937-53B7-4C00-80DB-5BBA5D567A81}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{AD0D3937-53B7-4C00-80DB-5BBA5D567A81}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="76">
   <si>
     <t>n°</t>
   </si>
@@ -171,13 +171,109 @@
   </si>
   <si>
     <t>Aderência</t>
+  </si>
+  <si>
+    <t>Conforme</t>
+  </si>
+  <si>
+    <t>Não Conforme</t>
+  </si>
+  <si>
+    <t>O nome "Elderia" está identificado no cabeçalho do quadro.</t>
+  </si>
+  <si>
+    <t>O nome é o mesmo em todos os artefatos, variando só a caixa ("ELDERIA" nos Artefatos 1 e 2 vs. "Elderia" aqui) — vale padronizar, mas não chega a ser uma não conformidade.</t>
+  </si>
+  <si>
+    <t>Cliente-alvo definido como "Profissionais da saúde e bem-estar e pacientes idosos".</t>
+  </si>
+  <si>
+    <t>O cliente-alvo é compatível com a proposta de conectar idosos a profissionais de saúde e bem-estar.</t>
+  </si>
+  <si>
+    <t>Categoria-segmento definida como "sistema facilitador de acesso ao serviço de profissionais da saúde e bem-estar".</t>
+  </si>
+  <si>
+    <t>A descrição da categoria situa bem o contexto de uso do produto.</t>
+  </si>
+  <si>
+    <t>Benefício-chave identificado: "Facilidade de acesso independente do idoso ao profissional".</t>
+  </si>
+  <si>
+    <t>O benefício representa uma necessidade real do público idoso: autonomia de acesso.</t>
+  </si>
+  <si>
+    <t>O benefício-chave está descrito de forma direta e objetiva.</t>
+  </si>
+  <si>
+    <t>Pelo mesmo motivo do item anterior, não dá para distinguir claramente o produto de soluções parecidas só com o que está escrito nesse campo.</t>
+  </si>
+  <si>
+    <t>A referência usada para comparação está identificada: "Sistemas de saúde geral".</t>
+  </si>
+  <si>
+    <t>O campo "Meta-valor" comunica o foco em atendimento especializado ao geriatra.</t>
+  </si>
+  <si>
+    <t>A proposta de valor comunica o benefício ao cliente-alvo, mesmo que de forma resumida.</t>
+  </si>
+  <si>
+    <t>Existe coerência entre cliente-alvo (idosos/profissionais), categoria (facilitador de acesso) e benefício-chave (acesso independente).</t>
+  </si>
+  <si>
+    <t>A coerência entre benefício, diferencial e proposta de valor fica prejudicada porque o campo do diferencial não descreve de fato um diferencial (ver itens 11 e 12).</t>
+  </si>
+  <si>
+    <t>Os cinco campos do quadro (Cliente-alvo, Categoria-segmento, Benefício-chave, Diferenciado-chave, Meta-valor) estão preenchidos.</t>
+  </si>
+  <si>
+    <t>O campo "Diferenciado-chave" fica ambíguo, já que o conteúdo dele é a referência comparativa, não o diferencial em si.</t>
+  </si>
+  <si>
+    <t>Encontramos inconsistência de nomenclatura: o rótulo "DIFERENCIADO-CHAVE" (adjetivo) foge do termo padrão "DIFERENCIAL-CHAVE" (substantivo) do modelo de Visão de Produto; o rótulo "META-VALOR." também tem um ponto final fora do padrão.</t>
+  </si>
+  <si>
+    <t>As características do cliente-alvo ("profissionais da saúde e bem-estar e pacientes idosos") deixam claro para quem o produto foi feito.</t>
+  </si>
+  <si>
+    <t>Médio</t>
+  </si>
+  <si>
+    <t>Baixo</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>Definir e registrar claramente o diferencial-chave do Elderia em relação aos sistemas de saúde gerais.</t>
+  </si>
+  <si>
+    <t>Detalhar as características e funcionalidades que tornam o Elderia diferente de outras soluções semelhantes.</t>
+  </si>
+  <si>
+    <t>Revisar os campos da Visão de Produto para garantir coerência entre o benefício-chave, o diferencial-chave e a proposta de valor</t>
+  </si>
+  <si>
+    <t>Enviado</t>
+  </si>
+  <si>
+    <t>Reformular o conteúdo do campo para apresentar claramente o diferencial do produto e eliminar ambiguidades.</t>
+  </si>
+  <si>
+    <t>Padronizar os rótulos do quadro, corrigindo “Diferenciado-chave” para “Diferencial-chave” e removendo o ponto final inadequado em “Meta-valor”.</t>
+  </si>
+  <si>
+    <t>O campo "Diferenciado-chave" traz só "Sistemas de saúde geral", que é a referência de comparação, mas não descreve o que de fato diferencia o Elderia dessas soluções.</t>
+  </si>
+  <si>
+    <t>Pierre</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -225,6 +321,13 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -264,10 +367,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -278,28 +382,34 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal 2" xfId="1" xr:uid="{7AD2918D-1C06-481B-AFD8-DC1952ACDB2F}"/>
   </cellStyles>
   <dxfs count="2">
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <font>
         <strike val="0"/>
@@ -320,9 +430,6 @@
         </patternFill>
       </fill>
     </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -337,10 +444,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{E6F584FC-A5BE-427A-BF40-6EFDB06653A1}" name="Table1" displayName="Table1" ref="B1:I21" totalsRowShown="0" headerRowDxfId="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{E6F584FC-A5BE-427A-BF40-6EFDB06653A1}" name="Table1" displayName="Table1" ref="B1:I21" totalsRowShown="0" headerRowDxfId="1">
   <autoFilter ref="B1:I21" xr:uid="{E6F584FC-A5BE-427A-BF40-6EFDB06653A1}"/>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{C491E1FB-C798-4CB3-80A6-3DFD3312A60E}" name="n°" dataDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{C491E1FB-C798-4CB3-80A6-3DFD3312A60E}" name="n°" dataDxfId="0"/>
     <tableColumn id="2" xr3:uid="{C3282D55-C28C-4600-82C6-FF827ED58CB0}" name="Descrição"/>
     <tableColumn id="3" xr3:uid="{993FF359-2EA1-48F1-8170-F50845F66692}" name="Resultado "/>
     <tableColumn id="4" xr3:uid="{8F145B2F-9B32-4493-893A-D425BEA70BEB}" name="Responsavel"/>
@@ -671,248 +778,609 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E750BC97-A7FF-445B-A9AC-9AC648705192}">
   <dimension ref="B1:I30"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="2" width="5.21875" customWidth="1"/>
-    <col min="3" max="3" width="76.44140625" customWidth="1"/>
-    <col min="4" max="4" width="19.5546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="13.77734375" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="5.1796875" customWidth="1"/>
+    <col min="3" max="3" width="78.1796875" customWidth="1"/>
+    <col min="4" max="4" width="19.54296875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.81640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="204.36328125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="21" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="18.88671875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="16.21875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="120.453125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="16.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B1" s="12" t="s">
+    <row r="1" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="E1" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="12" t="s">
+      <c r="F1" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="12" t="s">
+      <c r="G1" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="12" t="s">
+      <c r="H1" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="12" t="s">
+      <c r="I1" s="7" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B2" s="4">
         <v>1</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="3" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="D2" t="s">
+        <v>44</v>
+      </c>
+      <c r="E2" t="s">
+        <v>67</v>
+      </c>
+      <c r="F2" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="G2" t="s">
+        <v>67</v>
+      </c>
+      <c r="H2" t="s">
+        <v>67</v>
+      </c>
+      <c r="I2" s="8" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="3" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B3" s="4">
         <v>2</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="4" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="D3" t="s">
+        <v>44</v>
+      </c>
+      <c r="E3" t="s">
+        <v>67</v>
+      </c>
+      <c r="F3" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="G3" t="s">
+        <v>67</v>
+      </c>
+      <c r="H3" t="s">
+        <v>67</v>
+      </c>
+      <c r="I3" s="8" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="4" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B4" s="4">
         <v>3</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="5" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="D4" t="s">
+        <v>44</v>
+      </c>
+      <c r="E4" t="s">
+        <v>67</v>
+      </c>
+      <c r="F4" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="G4" t="s">
+        <v>67</v>
+      </c>
+      <c r="H4" t="s">
+        <v>67</v>
+      </c>
+      <c r="I4" s="8" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="5" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B5" s="4">
         <v>4</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="6" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="D5" t="s">
+        <v>44</v>
+      </c>
+      <c r="E5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F5" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="G5" t="s">
+        <v>67</v>
+      </c>
+      <c r="H5" t="s">
+        <v>67</v>
+      </c>
+      <c r="I5" s="8" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="6" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B6" s="4">
         <v>5</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="7" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="D6" t="s">
+        <v>44</v>
+      </c>
+      <c r="E6" t="s">
+        <v>67</v>
+      </c>
+      <c r="F6" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="G6" t="s">
+        <v>67</v>
+      </c>
+      <c r="H6" t="s">
+        <v>67</v>
+      </c>
+      <c r="I6" s="8" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="7" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B7" s="4">
         <v>6</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="8" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="D7" t="s">
+        <v>44</v>
+      </c>
+      <c r="E7" t="s">
+        <v>67</v>
+      </c>
+      <c r="F7" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="G7" t="s">
+        <v>67</v>
+      </c>
+      <c r="H7" t="s">
+        <v>67</v>
+      </c>
+      <c r="I7" s="8" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="8" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B8" s="4">
         <v>7</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="9" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="D8" t="s">
+        <v>44</v>
+      </c>
+      <c r="E8" t="s">
+        <v>67</v>
+      </c>
+      <c r="F8" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="G8" t="s">
+        <v>67</v>
+      </c>
+      <c r="H8" t="s">
+        <v>67</v>
+      </c>
+      <c r="I8" s="8" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="9" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B9" s="4">
         <v>8</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="10" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="D9" t="s">
+        <v>44</v>
+      </c>
+      <c r="E9" t="s">
+        <v>67</v>
+      </c>
+      <c r="F9" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="G9" t="s">
+        <v>67</v>
+      </c>
+      <c r="H9" t="s">
+        <v>67</v>
+      </c>
+      <c r="I9" s="8" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="10" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B10" s="4">
         <v>9</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="11" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="D10" t="s">
+        <v>44</v>
+      </c>
+      <c r="E10" t="s">
+        <v>67</v>
+      </c>
+      <c r="F10" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="G10" t="s">
+        <v>67</v>
+      </c>
+      <c r="H10" t="s">
+        <v>67</v>
+      </c>
+      <c r="I10" s="8" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="11" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B11" s="4">
         <v>10</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="12" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="D11" t="s">
+        <v>45</v>
+      </c>
+      <c r="E11" t="s">
+        <v>75</v>
+      </c>
+      <c r="F11" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="G11" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="H11" t="s">
+        <v>68</v>
+      </c>
+      <c r="I11" s="8" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="12" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B12" s="4">
         <v>11</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="13" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="D12" t="s">
+        <v>45</v>
+      </c>
+      <c r="E12" t="s">
+        <v>75</v>
+      </c>
+      <c r="F12" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="G12" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="H12" t="s">
+        <v>69</v>
+      </c>
+      <c r="I12" s="8" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="13" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B13" s="4">
         <v>12</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="14" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="D13" t="s">
+        <v>44</v>
+      </c>
+      <c r="E13" t="s">
+        <v>67</v>
+      </c>
+      <c r="F13" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="G13" t="s">
+        <v>67</v>
+      </c>
+      <c r="H13" t="s">
+        <v>67</v>
+      </c>
+      <c r="I13" s="8" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="14" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B14" s="4">
         <v>13</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="15" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="D14" t="s">
+        <v>44</v>
+      </c>
+      <c r="E14" t="s">
+        <v>67</v>
+      </c>
+      <c r="F14" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="G14" t="s">
+        <v>67</v>
+      </c>
+      <c r="H14" t="s">
+        <v>67</v>
+      </c>
+      <c r="I14" s="8" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="15" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B15" s="4">
         <v>14</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="16" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="D15" t="s">
+        <v>44</v>
+      </c>
+      <c r="E15" t="s">
+        <v>67</v>
+      </c>
+      <c r="F15" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="G15" t="s">
+        <v>67</v>
+      </c>
+      <c r="H15" t="s">
+        <v>67</v>
+      </c>
+      <c r="I15" s="8" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="16" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B16" s="4">
         <v>15</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="17" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="D16" t="s">
+        <v>44</v>
+      </c>
+      <c r="E16" t="s">
+        <v>67</v>
+      </c>
+      <c r="F16" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="G16" t="s">
+        <v>67</v>
+      </c>
+      <c r="H16" t="s">
+        <v>67</v>
+      </c>
+      <c r="I16" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="17" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B17" s="4">
         <v>16</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="18" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="D17" t="s">
+        <v>45</v>
+      </c>
+      <c r="E17" t="s">
+        <v>75</v>
+      </c>
+      <c r="F17" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="G17" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="H17" t="s">
+        <v>70</v>
+      </c>
+      <c r="I17" s="8" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="18" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B18" s="4">
         <v>17</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="19" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="D18" t="s">
+        <v>44</v>
+      </c>
+      <c r="E18" t="s">
+        <v>67</v>
+      </c>
+      <c r="F18" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="G18" t="s">
+        <v>67</v>
+      </c>
+      <c r="H18" t="s">
+        <v>67</v>
+      </c>
+      <c r="I18" s="8" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="19" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B19" s="4">
         <v>18</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="20" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="D19" t="s">
+        <v>45</v>
+      </c>
+      <c r="E19" t="s">
+        <v>75</v>
+      </c>
+      <c r="F19" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="G19" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="H19" t="s">
+        <v>72</v>
+      </c>
+      <c r="I19" s="8" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="20" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B20" s="4">
         <v>19</v>
       </c>
       <c r="C20" s="3" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="21" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="D20" t="s">
+        <v>45</v>
+      </c>
+      <c r="E20" t="s">
+        <v>75</v>
+      </c>
+      <c r="F20" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="G20" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="H20" t="s">
+        <v>73</v>
+      </c>
+      <c r="I20" s="8" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="21" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B21" s="4">
         <v>20</v>
       </c>
       <c r="C21" s="3" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="23" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C23" s="11" t="s">
+      <c r="D21" t="s">
+        <v>44</v>
+      </c>
+      <c r="E21" t="s">
+        <v>67</v>
+      </c>
+      <c r="F21" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="G21" t="s">
+        <v>67</v>
+      </c>
+      <c r="H21" t="s">
+        <v>67</v>
+      </c>
+      <c r="I21" s="8" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="23" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="C23" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="D23" s="11"/>
-      <c r="F23" s="6" t="s">
+      <c r="D23" s="6"/>
+      <c r="F23" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="G23" s="6"/>
-      <c r="H23" s="6"/>
-      <c r="I23" s="6"/>
-    </row>
-    <row r="24" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="G23" s="10"/>
+      <c r="H23" s="10"/>
+      <c r="I23" s="10"/>
+    </row>
+    <row r="24" spans="2:9" x14ac:dyDescent="0.35">
       <c r="C24" s="5" t="s">
         <v>29</v>
       </c>
       <c r="D24" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="F24" s="7" t="s">
+      <c r="F24" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="G24" s="8" t="s">
+      <c r="G24" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="H24" s="7" t="s">
+      <c r="H24" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="I24" s="8" t="s">
+      <c r="I24" s="13" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="25" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:9" x14ac:dyDescent="0.35">
       <c r="C25" s="5" t="s">
         <v>31</v>
       </c>
       <c r="D25" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="F25" s="9"/>
-      <c r="G25" s="10"/>
-      <c r="H25" s="9"/>
-      <c r="I25" s="10"/>
-    </row>
-    <row r="26" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="F25" s="12"/>
+      <c r="G25" s="14"/>
+      <c r="H25" s="12"/>
+      <c r="I25" s="14"/>
+    </row>
+    <row r="26" spans="2:9" x14ac:dyDescent="0.35">
       <c r="C26" s="5" t="s">
         <v>33</v>
       </c>
@@ -920,23 +1388,23 @@
         <v>34</v>
       </c>
       <c r="F26" s="5">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G26" s="5">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="H26" s="5">
         <v>0</v>
       </c>
-      <c r="I26" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I26" s="9">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="27" spans="2:9" x14ac:dyDescent="0.35">
       <c r="C27" s="5"/>
       <c r="D27" s="5"/>
     </row>
-    <row r="28" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:9" x14ac:dyDescent="0.35">
       <c r="C28" s="5" t="s">
         <v>35</v>
       </c>
@@ -944,13 +1412,13 @@
         <v>38</v>
       </c>
     </row>
-    <row r="29" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:9" x14ac:dyDescent="0.35">
       <c r="C29" s="5" t="s">
         <v>36</v>
       </c>
       <c r="D29" s="5"/>
     </row>
-    <row r="30" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:9" x14ac:dyDescent="0.35">
       <c r="C30" s="5" t="s">
         <v>37</v>
       </c>
@@ -973,14 +1441,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="aed73f09-bf5d-4147-a3d9-eca4840d3416" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101007CCF20922A0DE34DA3357EDA40AE3850" ma:contentTypeVersion="5" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="df2c289d3a08b18055ba2ef47a57998b">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="aed73f09-bf5d-4147-a3d9-eca4840d3416" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="91dac5f1c2bd6141b57005fd2a16424c" ns3:_="">
     <xsd:import namespace="aed73f09-bf5d-4147-a3d9-eca4840d3416"/>
@@ -1130,7 +1590,7 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -1139,23 +1599,15 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F1DD7AEA-0F16-4812-9CB4-B4A9D955A9E2}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="aed73f09-bf5d-4147-a3d9-eca4840d3416"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="aed73f09-bf5d-4147-a3d9-eca4840d3416" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C9516A9F-BD2F-4061-A991-438BE9F7F39C}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1173,7 +1625,7 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C39528C1-3F3D-4F42-8119-936F8AFAB22A}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
@@ -1181,8 +1633,25 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F1DD7AEA-0F16-4812-9CB4-B4A9D955A9E2}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="aed73f09-bf5d-4147-a3d9-eca4840d3416"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{19540963-e559-4020-8a90-fe8a502c2801}" enabled="1" method="Standard" siteId="{f25493ae-1c98-41d7-8a33-0be75f5fe603}" contentBits="0" removed="0"/>
   <clbl:label id="{8a1ef6c3-8324-4103-bf4a-1328c5dc3653}" enabled="0" method="" siteId="{8a1ef6c3-8324-4103-bf4a-1328c5dc3653}" removed="1"/>
 </clbl:labelList>
 </file>